--- a/artfynd/A 7034-2026 artfynd.xlsx
+++ b/artfynd/A 7034-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128464864</v>
+        <v>128465650</v>
       </c>
       <c r="B2" t="n">
-        <v>90285</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>245031</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Borgsjömusseron</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tricholoma borgsjoeënse</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Jacobsson &amp; Muskos</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>402538</v>
+        <v>402436</v>
       </c>
       <c r="R2" t="n">
-        <v>7041348</v>
+        <v>7041567</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,45 +777,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128465311</v>
+        <v>128464424</v>
       </c>
       <c r="B3" t="n">
-        <v>91533</v>
+        <v>92632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Husådalen, Husådalen, Jmt</t>
+          <t>Knogevallen, Knogevallen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>402526</v>
+        <v>402708</v>
       </c>
       <c r="R3" t="n">
-        <v>7041492</v>
+        <v>7041497</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128464424</v>
+        <v>128465176</v>
       </c>
       <c r="B4" t="n">
-        <v>92213</v>
+        <v>89143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,34 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>4405</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Knogevallen, Knogevallen, Jmt</t>
+          <t>Husådalen, Husådalen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>402708</v>
+        <v>402489</v>
       </c>
       <c r="R4" t="n">
-        <v>7041497</v>
+        <v>7041319</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128465176</v>
+        <v>128464240</v>
       </c>
       <c r="B5" t="n">
-        <v>88766</v>
+        <v>92869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,34 +992,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4405</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Husådalen, Husådalen, Jmt</t>
+          <t>Knogevallen, Knogevallen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>402489</v>
+        <v>402865</v>
       </c>
       <c r="R5" t="n">
-        <v>7041319</v>
+        <v>7041486</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128465650</v>
+        <v>128464550</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>83307</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,34 +1094,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Husådalen, Husådalen, Jmt</t>
+          <t>Knogevallen, Knogevallen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>402436</v>
+        <v>402667</v>
       </c>
       <c r="R6" t="n">
-        <v>7041567</v>
+        <v>7041515</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128464550</v>
+        <v>128464412</v>
       </c>
       <c r="B7" t="n">
-        <v>83005</v>
+        <v>78339</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>402667</v>
+        <v>402730</v>
       </c>
       <c r="R7" t="n">
-        <v>7041515</v>
+        <v>7041493</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,45 +1287,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128464240</v>
+        <v>128464864</v>
       </c>
       <c r="B8" t="n">
-        <v>92451</v>
+        <v>90668</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4769</v>
+        <v>245031</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Borgsjömusseron</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Tricholoma borgsjoeënse</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Jacobsson &amp; Muskos</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Knogevallen, Knogevallen, Jmt</t>
+          <t>Husådalen, Husådalen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>402865</v>
+        <v>402538</v>
       </c>
       <c r="R8" t="n">
-        <v>7041486</v>
+        <v>7041348</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,108 +1386,6 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>128464412</v>
-      </c>
-      <c r="B9" t="n">
-        <v>78042</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>228579</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Liten svartspik</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Chaenothecopsis nana</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Knogevallen, Knogevallen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>402730</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7041493</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Kall</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2025-09-15</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2025-09-15</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Bördig, örtrik granskog med grässvål, naturskogsartat</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7034-2026 artfynd.xlsx
+++ b/artfynd/A 7034-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128464424</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465176</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128464240</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465650</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128464550</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128464412</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,8 +1421,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128464864</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>